--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_17-11-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_17-11-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -574,26 +574,26 @@
       <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -684,26 +684,26 @@
       <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -794,26 +794,26 @@
       <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -904,26 +904,26 @@
       <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1014,26 +1014,26 @@
       <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1124,26 +1124,26 @@
       <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.47</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.47</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.47</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1234,26 +1234,26 @@
       <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1344,26 +1344,26 @@
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1454,26 +1454,26 @@
       <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1564,26 +1564,26 @@
       <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1674,26 +1674,26 @@
       <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£30.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1784,26 +1784,26 @@
       <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.70</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.70</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1894,26 +1894,26 @@
       <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2004,26 +2004,26 @@
       <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2114,26 +2114,26 @@
       <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff79e93a235
+	0x7ff79e692650
+	0x7ff79e4216dd
+	0x7ff79e47a27e
+	0x7ff79e47a58c
+	0x7ff79e4ced77
+	0x7ff79e4cbaba
+	0x7ff79e46b0ed
+	0x7ff79e46bf63
+	0x7ff79e965d60
+	0x7ff79e95fe8a
+	0x7ff79e981005
+	0x7ff79e6ad73e
+	0x7ff79e6b4e3f
+	0x7ff79e69b7e4
+	0x7ff79e69b99f
+	0x7ff79e681908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
